--- a/Outputs/3_DSFI_value_checker.xlsx
+++ b/Outputs/3_DSFI_value_checker.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="8_{A4D23877-DF11-4FDF-8CDC-609C28C55F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B5E8E4C-DB55-4C4C-A83D-AA194D775390}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F67964B0-4977-45D6-823C-78EBA3F89259}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{F67964B0-4977-45D6-823C-78EBA3F89259}"/>
   </bookViews>
   <sheets>
     <sheet name="DSFI CHECK v8 2022" sheetId="1" r:id="rId1"/>
@@ -1194,7 +1194,7 @@
         <v>4</v>
       </c>
       <c r="N3" t="b">
-        <f t="shared" ref="N2:N33" si="1">IF(M3&gt;0, K3=M3, IF(L3&gt;0, K3=L3, "BLANK"))</f>
+        <f t="shared" ref="N3:N33" si="1">IF(M3&gt;0, K3=M3, IF(L3&gt;0, K3=L3, "BLANK"))</f>
         <v>1</v>
       </c>
       <c r="O3" t="s">

--- a/Outputs/3_DSFI_value_checker.xlsx
+++ b/Outputs/3_DSFI_value_checker.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="8_{A4D23877-DF11-4FDF-8CDC-609C28C55F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B5E8E4C-DB55-4C4C-A83D-AA194D775390}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{F67964B0-4977-45D6-823C-78EBA3F89259}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{F67964B0-4977-45D6-823C-78EBA3F89259}"/>
   </bookViews>
   <sheets>
     <sheet name="DSFI CHECK v8 2022" sheetId="1" r:id="rId1"/>
@@ -1029,26 +1029,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B62A0E1-FCA7-4C2A-8A1C-2B336E54F032}">
   <dimension ref="A1:S98"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.5234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.734375" customWidth="1"/>
-    <col min="6" max="6" width="16.47265625" customWidth="1"/>
-    <col min="7" max="7" width="11.15625" customWidth="1"/>
+    <col min="1" max="1" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.7265625" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="13.5234375" customWidth="1"/>
-    <col min="10" max="10" width="13.7890625" customWidth="1"/>
-    <col min="11" max="11" width="11.5234375" customWidth="1"/>
-    <col min="12" max="12" width="18.47265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.47265625" customWidth="1"/>
-    <col min="14" max="14" width="8.26171875" customWidth="1"/>
-    <col min="15" max="15" width="18.734375" customWidth="1"/>
-    <col min="18" max="19" width="8.734375" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" customWidth="1"/>
+    <col min="12" max="12" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.453125" customWidth="1"/>
+    <col min="14" max="14" width="8.26953125" customWidth="1"/>
+    <col min="15" max="15" width="18.7265625" customWidth="1"/>
+    <col min="18" max="19" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>50</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>62</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>64</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>72</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>96</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>98</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>100</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>106</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>108</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>110</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>112</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>114</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>116</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>118</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>120</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>122</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>124</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>126</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>128</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>130</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>132</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>134</v>
       </c>
@@ -3938,7 +3938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>136</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>138</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>140</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>142</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>144</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>146</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>148</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>150</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>152</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>154</v>
       </c>
@@ -4407,7 +4407,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>156</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>158</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>160</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>162</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>164</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>166</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>168</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>170</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>172</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>174</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>176</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>178</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>180</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>182</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>184</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>186</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>188</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>190</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>192</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>194</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>196</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>198</v>
       </c>
@@ -5437,7 +5437,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>200</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>202</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>206</v>
       </c>
